--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:14:04+00:00</t>
+    <t>2026-08-31T21:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:22:01+00:00</t>
+    <t>2026-08-31T21:48:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T21:48:04+00:00</t>
+    <t>2026-08-31T22:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="101">
   <si>
     <t>Property</t>
   </si>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T22:00:30+00:00</t>
+    <t>2026-09-01T09:07:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -136,7 +136,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>Code</t>
@@ -256,6 +256,12 @@
   </si>
   <si>
     <t>Version 1.7.2 Ablehnung</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.3.1937.777.24.2.4055</t>
+  </si>
+  <si>
+    <t>Version 1.7.2 Vertretende</t>
   </si>
   <si>
     <t>2.16.840.1.113883.3.1937.777.24.2.2722</t>
@@ -705,7 +711,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -916,21 +922,21 @@
       <c r="C17" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="D17" t="s" s="2">
-        <v>90</v>
-      </c>
+      <c r="D17" s="2"/>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
         <v>55</v>
       </c>
       <c r="B18" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="C18" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="C18" t="s" s="2">
+      <c r="D18" t="s" s="2">
         <v>92</v>
       </c>
-      <c r="D18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
@@ -967,6 +973,18 @@
         <v>98</v>
       </c>
       <c r="D21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="C22" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="D22" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T09:07:35+00:00</t>
+    <t>2026-09-04T10:28:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:28:22+00:00</t>
+    <t>2026-09-04T11:15:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:15:21+00:00</t>
+    <t>2026-09-04T11:42:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:42:10+00:00</t>
+    <t>2026-09-04T11:52:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:52:09+00:00</t>
+    <t>2026-09-04T12:01:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:01:13+00:00</t>
+    <t>2026-09-04T12:10:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -136,7 +136,7 @@
     <t>Count</t>
   </si>
   <si>
-    <t>21</t>
+    <t>20</t>
   </si>
   <si>
     <t>Code</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:10:03+00:00</t>
+    <t>2026-09-04T12:19:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/migration/2027.0.0-ballot.rc1-template-v0.13.2/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T12:19:56+00:00</t>
+    <t>2026-09-04T13:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
